--- a/01_test_base/Средства для тестов.xlsx
+++ b/01_test_base/Средства для тестов.xlsx
@@ -2082,7 +2082,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="25.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="18.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="18" style="1" width="48.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="38.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="43.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="72.97"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1022" min="24" style="1" width="15.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1023" style="1" width="11.52"/>
@@ -3655,7 +3655,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="15.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.70703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="26.32"/>
@@ -4076,7 +4076,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="15.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.70703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="23.27"/>
@@ -4598,7 +4598,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="15.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.70703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="29.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="23.69"/>
@@ -4773,7 +4773,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="12.578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.52"/>
